--- a/sample.xlsx
+++ b/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project_clone\nuclass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE014C2-4290-4B28-9AEE-BA0A42C744C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789B8A63-907F-4ED4-B791-B32F4CDA9083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86ED655E-D6BD-4E2D-8E5E-29F626CB4542}"/>
   </bookViews>
@@ -5658,10 +5658,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A118" s="2" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>482</v>
@@ -5670,10 +5670,10 @@
         <v>2</v>
       </c>
       <c r="E118" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F118" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>482</v>
@@ -5682,18 +5682,18 @@
         <v>0</v>
       </c>
       <c r="I118" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J118" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A119" s="2" t="s">
-        <v>427</v>
+        <v>329</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>482</v>
@@ -5705,7 +5705,7 @@
         <v>5</v>
       </c>
       <c r="F119" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>482</v>
@@ -5714,18 +5714,18 @@
         <v>0</v>
       </c>
       <c r="I119" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J119" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A120" s="2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>482</v>
@@ -5737,7 +5737,7 @@
         <v>5</v>
       </c>
       <c r="F120" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>482</v>
@@ -5746,18 +5746,18 @@
         <v>0</v>
       </c>
       <c r="I120" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J120" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A121" s="2" t="s">
-        <v>315</v>
+        <v>418</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>482</v>
@@ -5769,7 +5769,7 @@
         <v>5</v>
       </c>
       <c r="F121" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>482</v>
@@ -5778,18 +5778,18 @@
         <v>0</v>
       </c>
       <c r="I121" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J121" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A122" s="2" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>482</v>
@@ -5801,7 +5801,7 @@
         <v>5</v>
       </c>
       <c r="F122" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>482</v>
@@ -5810,18 +5810,18 @@
         <v>0</v>
       </c>
       <c r="I122" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J122" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A123" s="2" t="s">
-        <v>382</v>
+        <v>243</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>482</v>
@@ -5833,7 +5833,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>482</v>
@@ -5842,18 +5842,18 @@
         <v>0</v>
       </c>
       <c r="I123" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J123" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A124" s="2" t="s">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>482</v>
@@ -5865,7 +5865,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>482</v>
@@ -5874,18 +5874,18 @@
         <v>0</v>
       </c>
       <c r="I124" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J124" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A125" s="2" t="s">
-        <v>298</v>
+        <v>405</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>482</v>
@@ -5897,7 +5897,7 @@
         <v>5</v>
       </c>
       <c r="F125" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>482</v>
@@ -5906,18 +5906,18 @@
         <v>0</v>
       </c>
       <c r="I125" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J125" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A126" s="2" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>482</v>
@@ -5929,27 +5929,27 @@
         <v>5</v>
       </c>
       <c r="F126" s="3">
+        <v>9</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3">
         <v>8</v>
       </c>
-      <c r="G126" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I126" s="3">
-        <v>6</v>
-      </c>
       <c r="J126" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A127" s="2" t="s">
-        <v>458</v>
+        <v>308</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>482</v>
@@ -5961,7 +5961,7 @@
         <v>5</v>
       </c>
       <c r="F127" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>482</v>
@@ -5970,18 +5970,18 @@
         <v>0</v>
       </c>
       <c r="I127" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J127" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A128" s="2" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>482</v>
@@ -5993,7 +5993,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>482</v>
@@ -6002,18 +6002,18 @@
         <v>0</v>
       </c>
       <c r="I128" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J128" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A129" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>482</v>
@@ -6025,7 +6025,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>482</v>
@@ -6037,15 +6037,15 @@
         <v>1</v>
       </c>
       <c r="J129" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A130" s="2" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>482</v>
@@ -6057,7 +6057,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>482</v>
@@ -6066,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J130" s="3">
         <v>8</v>
@@ -6074,10 +6074,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A131" s="2" t="s">
-        <v>333</v>
+        <v>468</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>482</v>
@@ -6089,7 +6089,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>482</v>
@@ -6098,18 +6098,18 @@
         <v>0</v>
       </c>
       <c r="I131" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J131" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A132" s="2" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>482</v>
@@ -6121,7 +6121,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>482</v>
@@ -6133,15 +6133,15 @@
         <v>8</v>
       </c>
       <c r="J132" s="3">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A133" s="2" t="s">
-        <v>452</v>
+        <v>320</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>216</v>
+        <v>86</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>482</v>
@@ -6153,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="F133" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>482</v>
@@ -6162,18 +6162,18 @@
         <v>0</v>
       </c>
       <c r="I133" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J133" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A134" s="2" t="s">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>482</v>
@@ -6185,7 +6185,7 @@
         <v>5</v>
       </c>
       <c r="F134" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>482</v>
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J134" s="3">
         <v>24</v>
@@ -6202,10 +6202,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A135" s="2" t="s">
-        <v>261</v>
+        <v>420</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>482</v>
@@ -6217,7 +6217,7 @@
         <v>5</v>
       </c>
       <c r="F135" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>482</v>
@@ -6226,18 +6226,18 @@
         <v>0</v>
       </c>
       <c r="I135" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J135" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A136" s="2" t="s">
-        <v>420</v>
+        <v>471</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>482</v>
@@ -6249,7 +6249,7 @@
         <v>5</v>
       </c>
       <c r="F136" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>482</v>
@@ -6258,18 +6258,18 @@
         <v>0</v>
       </c>
       <c r="I136" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J136" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A137" s="2" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>482</v>
@@ -6281,7 +6281,7 @@
         <v>5</v>
       </c>
       <c r="F137" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>482</v>
@@ -6293,15 +6293,15 @@
         <v>8</v>
       </c>
       <c r="J137" s="3">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A138" s="2" t="s">
-        <v>454</v>
+        <v>284</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>218</v>
+        <v>50</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>482</v>
@@ -6313,7 +6313,7 @@
         <v>5</v>
       </c>
       <c r="F138" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>482</v>
@@ -6322,18 +6322,18 @@
         <v>0</v>
       </c>
       <c r="I138" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J138" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A139" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>482</v>
@@ -6345,7 +6345,7 @@
         <v>5</v>
       </c>
       <c r="F139" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>482</v>
@@ -6354,18 +6354,18 @@
         <v>0</v>
       </c>
       <c r="I139" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J139" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A140" s="2" t="s">
-        <v>302</v>
+        <v>426</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>482</v>
@@ -6377,7 +6377,7 @@
         <v>5</v>
       </c>
       <c r="F140" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>482</v>
@@ -6386,18 +6386,18 @@
         <v>0</v>
       </c>
       <c r="I140" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J140" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A141" s="2" t="s">
-        <v>426</v>
+        <v>260</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>482</v>
@@ -6409,27 +6409,27 @@
         <v>5</v>
       </c>
       <c r="F141" s="3">
+        <v>24</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I141" s="3">
+        <v>1</v>
+      </c>
+      <c r="J141" s="3">
         <v>23</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H141" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I141" s="3">
-        <v>7</v>
-      </c>
-      <c r="J141" s="3">
-        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A142" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>482</v>
@@ -6441,7 +6441,7 @@
         <v>5</v>
       </c>
       <c r="F142" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>482</v>
@@ -6450,18 +6450,18 @@
         <v>0</v>
       </c>
       <c r="I142" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J142" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A143" s="2" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>482</v>
@@ -6473,7 +6473,7 @@
         <v>5</v>
       </c>
       <c r="F143" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>482</v>
@@ -6482,18 +6482,18 @@
         <v>0</v>
       </c>
       <c r="I143" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J143" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A144" s="2" t="s">
-        <v>304</v>
+        <v>400</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>482</v>
@@ -6505,7 +6505,7 @@
         <v>5</v>
       </c>
       <c r="F144" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>482</v>
@@ -6514,18 +6514,18 @@
         <v>0</v>
       </c>
       <c r="I144" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J144" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A145" s="2" t="s">
-        <v>400</v>
+        <v>238</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>482</v>
@@ -6537,7 +6537,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>482</v>
@@ -6546,18 +6546,18 @@
         <v>0</v>
       </c>
       <c r="I145" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J145" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A146" s="2" t="s">
-        <v>238</v>
+        <v>293</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>482</v>
@@ -6569,7 +6569,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>482</v>
@@ -6578,18 +6578,18 @@
         <v>0</v>
       </c>
       <c r="I146" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A147" s="2" t="s">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>482</v>
@@ -6598,30 +6598,30 @@
         <v>2</v>
       </c>
       <c r="E147" s="3">
+        <v>6</v>
+      </c>
+      <c r="F147" s="3">
+        <v>1</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I147" s="3">
         <v>5</v>
       </c>
-      <c r="F147" s="3">
-        <v>29</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H147" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I147" s="3">
-        <v>2</v>
-      </c>
       <c r="J147" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A148" s="2" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>482</v>
@@ -6633,7 +6633,7 @@
         <v>6</v>
       </c>
       <c r="F148" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>482</v>
@@ -6645,15 +6645,15 @@
         <v>5</v>
       </c>
       <c r="J148" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A149" s="2" t="s">
-        <v>383</v>
+        <v>250</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>482</v>
@@ -6665,7 +6665,7 @@
         <v>6</v>
       </c>
       <c r="F149" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>482</v>
@@ -6674,18 +6674,18 @@
         <v>0</v>
       </c>
       <c r="I149" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J149" s="3">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A150" s="2" t="s">
-        <v>250</v>
+        <v>349</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>482</v>
@@ -6697,7 +6697,7 @@
         <v>6</v>
       </c>
       <c r="F150" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>482</v>
@@ -6706,18 +6706,18 @@
         <v>0</v>
       </c>
       <c r="I150" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J150" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A151" s="2" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>482</v>
@@ -6729,7 +6729,7 @@
         <v>6</v>
       </c>
       <c r="F151" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>482</v>
@@ -6738,18 +6738,18 @@
         <v>0</v>
       </c>
       <c r="I151" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J151" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A152" s="2" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>482</v>
@@ -6761,7 +6761,7 @@
         <v>6</v>
       </c>
       <c r="F152" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>482</v>
@@ -6770,18 +6770,18 @@
         <v>0</v>
       </c>
       <c r="I152" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J152" s="3">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A153" s="2" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>482</v>
@@ -6793,27 +6793,27 @@
         <v>6</v>
       </c>
       <c r="F153" s="3">
+        <v>7</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I153" s="3">
         <v>6</v>
       </c>
-      <c r="G153" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H153" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I153" s="3">
-        <v>7</v>
-      </c>
       <c r="J153" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A154" s="2" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>482</v>
@@ -6825,27 +6825,27 @@
         <v>6</v>
       </c>
       <c r="F154" s="3">
+        <v>8</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I154" s="3">
         <v>7</v>
       </c>
-      <c r="G154" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I154" s="3">
-        <v>6</v>
-      </c>
       <c r="J154" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A155" s="2" t="s">
-        <v>442</v>
+        <v>269</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>482</v>
@@ -6857,7 +6857,7 @@
         <v>6</v>
       </c>
       <c r="F155" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>482</v>
@@ -6866,18 +6866,18 @@
         <v>0</v>
       </c>
       <c r="I155" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J155" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A156" s="2" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>482</v>
@@ -6889,7 +6889,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>482</v>
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J156" s="3">
         <v>3</v>
@@ -6906,10 +6906,10 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A157" s="2" t="s">
-        <v>358</v>
+        <v>299</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>482</v>
@@ -6921,7 +6921,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>482</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J157" s="3">
         <v>3</v>
@@ -6938,10 +6938,10 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A158" s="2" t="s">
-        <v>299</v>
+        <v>412</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>482</v>
@@ -6953,7 +6953,7 @@
         <v>6</v>
       </c>
       <c r="F158" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>482</v>
@@ -6962,18 +6962,18 @@
         <v>0</v>
       </c>
       <c r="I158" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J158" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A159" s="2" t="s">
-        <v>412</v>
+        <v>348</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>177</v>
+        <v>114</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>482</v>
@@ -6985,7 +6985,7 @@
         <v>6</v>
       </c>
       <c r="F159" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>482</v>
@@ -6994,18 +6994,18 @@
         <v>0</v>
       </c>
       <c r="I159" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J159" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A160" s="2" t="s">
-        <v>348</v>
+        <v>428</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>482</v>
@@ -7017,7 +7017,7 @@
         <v>6</v>
       </c>
       <c r="F160" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>482</v>
@@ -7026,18 +7026,18 @@
         <v>0</v>
       </c>
       <c r="I160" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J160" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A161" s="2" t="s">
-        <v>428</v>
+        <v>324</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>482</v>
@@ -7049,7 +7049,7 @@
         <v>6</v>
       </c>
       <c r="F161" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>482</v>
@@ -7058,18 +7058,18 @@
         <v>0</v>
       </c>
       <c r="I161" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J161" s="3">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A162" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>482</v>
@@ -7081,7 +7081,7 @@
         <v>6</v>
       </c>
       <c r="F162" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>482</v>
@@ -7090,18 +7090,18 @@
         <v>0</v>
       </c>
       <c r="I162" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J162" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A163" s="2" t="s">
-        <v>327</v>
+        <v>444</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>93</v>
+        <v>208</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>482</v>
@@ -7113,7 +7113,7 @@
         <v>6</v>
       </c>
       <c r="F163" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>482</v>
@@ -7122,18 +7122,18 @@
         <v>0</v>
       </c>
       <c r="I163" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J163" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A164" s="2" t="s">
-        <v>444</v>
+        <v>331</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>208</v>
+        <v>97</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>482</v>
@@ -7145,7 +7145,7 @@
         <v>6</v>
       </c>
       <c r="F164" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>482</v>
@@ -7154,18 +7154,18 @@
         <v>0</v>
       </c>
       <c r="I164" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J164" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A165" s="2" t="s">
-        <v>331</v>
+        <v>472</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>482</v>
@@ -7177,7 +7177,7 @@
         <v>6</v>
       </c>
       <c r="F165" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>482</v>
@@ -7186,18 +7186,18 @@
         <v>0</v>
       </c>
       <c r="I165" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J165" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A166" s="2" t="s">
-        <v>472</v>
+        <v>277</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>236</v>
+        <v>44</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>482</v>
@@ -7209,7 +7209,7 @@
         <v>6</v>
       </c>
       <c r="F166" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>482</v>
@@ -7218,18 +7218,18 @@
         <v>0</v>
       </c>
       <c r="I166" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J166" s="3">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A167" s="2" t="s">
-        <v>277</v>
+        <v>388</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>482</v>
@@ -7241,7 +7241,7 @@
         <v>6</v>
       </c>
       <c r="F167" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>482</v>
@@ -7250,18 +7250,18 @@
         <v>0</v>
       </c>
       <c r="I167" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J167" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A168" s="2" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>482</v>
@@ -7273,7 +7273,7 @@
         <v>6</v>
       </c>
       <c r="F168" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>482</v>
@@ -7282,18 +7282,18 @@
         <v>0</v>
       </c>
       <c r="I168" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J168" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A169" s="2" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>482</v>
@@ -7305,7 +7305,7 @@
         <v>6</v>
       </c>
       <c r="F169" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>482</v>
@@ -7314,18 +7314,18 @@
         <v>0</v>
       </c>
       <c r="I169" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J169" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A170" s="2" t="s">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>482</v>
@@ -7337,7 +7337,7 @@
         <v>6</v>
       </c>
       <c r="F170" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>482</v>
@@ -7346,18 +7346,18 @@
         <v>0</v>
       </c>
       <c r="I170" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J170" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A171" s="2" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>482</v>
@@ -7369,7 +7369,7 @@
         <v>6</v>
       </c>
       <c r="F171" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>482</v>
@@ -7378,18 +7378,18 @@
         <v>0</v>
       </c>
       <c r="I171" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J171" s="3">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A172" s="2" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>482</v>
@@ -7401,7 +7401,7 @@
         <v>6</v>
       </c>
       <c r="F172" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>482</v>
@@ -7410,18 +7410,18 @@
         <v>0</v>
       </c>
       <c r="I172" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J172" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A173" s="2" t="s">
-        <v>423</v>
+        <v>242</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>482</v>
@@ -7433,7 +7433,7 @@
         <v>6</v>
       </c>
       <c r="F173" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>482</v>
@@ -7442,18 +7442,18 @@
         <v>0</v>
       </c>
       <c r="I173" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J173" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A174" s="2" t="s">
-        <v>242</v>
+        <v>443</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>482</v>
@@ -7474,18 +7474,18 @@
         <v>0</v>
       </c>
       <c r="I174" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J174" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A175" s="2" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>207</v>
+        <v>37</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>482</v>
@@ -7497,7 +7497,7 @@
         <v>6</v>
       </c>
       <c r="F175" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>482</v>
@@ -7506,18 +7506,18 @@
         <v>0</v>
       </c>
       <c r="I175" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J175" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A176" s="2" t="s">
-        <v>270</v>
+        <v>379</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>482</v>
@@ -7526,10 +7526,10 @@
         <v>2</v>
       </c>
       <c r="E176" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F176" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>482</v>
@@ -7538,18 +7538,18 @@
         <v>0</v>
       </c>
       <c r="I176" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J176" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A177" s="2" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>482</v>
@@ -7561,7 +7561,7 @@
         <v>7</v>
       </c>
       <c r="F177" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>482</v>
@@ -7570,18 +7570,18 @@
         <v>0</v>
       </c>
       <c r="I177" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J177" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A178" s="2" t="s">
-        <v>387</v>
+        <v>311</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>482</v>
@@ -7593,7 +7593,7 @@
         <v>7</v>
       </c>
       <c r="F178" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>482</v>
@@ -7602,18 +7602,18 @@
         <v>0</v>
       </c>
       <c r="I178" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J178" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A179" s="2" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>482</v>
@@ -7625,7 +7625,7 @@
         <v>7</v>
       </c>
       <c r="F179" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>482</v>
@@ -7634,18 +7634,18 @@
         <v>0</v>
       </c>
       <c r="I179" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J179" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A180" s="2" t="s">
-        <v>343</v>
+        <v>470</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>482</v>
@@ -7657,7 +7657,7 @@
         <v>7</v>
       </c>
       <c r="F180" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>482</v>
@@ -7666,18 +7666,18 @@
         <v>0</v>
       </c>
       <c r="I180" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J180" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A181" s="2" t="s">
-        <v>470</v>
+        <v>309</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>482</v>
@@ -7689,7 +7689,7 @@
         <v>7</v>
       </c>
       <c r="F181" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>482</v>
@@ -7698,18 +7698,18 @@
         <v>0</v>
       </c>
       <c r="I181" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J181" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A182" s="2" t="s">
-        <v>309</v>
+        <v>459</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>482</v>
@@ -7721,7 +7721,7 @@
         <v>7</v>
       </c>
       <c r="F182" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>482</v>
@@ -7730,18 +7730,18 @@
         <v>0</v>
       </c>
       <c r="I182" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J182" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A183" s="2" t="s">
-        <v>459</v>
+        <v>341</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>482</v>
@@ -7753,7 +7753,7 @@
         <v>7</v>
       </c>
       <c r="F183" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>482</v>
@@ -7762,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="I183" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J183" s="3">
         <v>16</v>
@@ -7770,10 +7770,10 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A184" s="2" t="s">
-        <v>341</v>
+        <v>254</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>482</v>
@@ -7785,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="F184" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>482</v>
@@ -7794,18 +7794,18 @@
         <v>0</v>
       </c>
       <c r="I184" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J184" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A185" s="2" t="s">
-        <v>254</v>
+        <v>456</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>482</v>
@@ -7817,7 +7817,7 @@
         <v>7</v>
       </c>
       <c r="F185" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>482</v>
@@ -7826,18 +7826,18 @@
         <v>0</v>
       </c>
       <c r="I185" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J185" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A186" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>482</v>
@@ -7849,7 +7849,7 @@
         <v>7</v>
       </c>
       <c r="F186" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>482</v>
@@ -7861,15 +7861,15 @@
         <v>8</v>
       </c>
       <c r="J186" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A187" s="2" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>482</v>
@@ -7881,7 +7881,7 @@
         <v>7</v>
       </c>
       <c r="F187" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>482</v>
@@ -7890,18 +7890,18 @@
         <v>0</v>
       </c>
       <c r="I187" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J187" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A188" s="2" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>482</v>
@@ -7913,7 +7913,7 @@
         <v>7</v>
       </c>
       <c r="F188" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>482</v>
@@ -7922,18 +7922,18 @@
         <v>0</v>
       </c>
       <c r="I188" s="3">
+        <v>6</v>
+      </c>
+      <c r="J188" s="3">
         <v>7</v>
-      </c>
-      <c r="J188" s="3">
-        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A189" s="2" t="s">
-        <v>391</v>
+        <v>303</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>482</v>
@@ -7945,7 +7945,7 @@
         <v>7</v>
       </c>
       <c r="F189" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>482</v>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="I189" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J189" s="3">
         <v>7</v>
@@ -7962,10 +7962,10 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A190" s="2" t="s">
-        <v>303</v>
+        <v>424</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>482</v>
@@ -7977,7 +7977,7 @@
         <v>7</v>
       </c>
       <c r="F190" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>482</v>
@@ -7986,18 +7986,18 @@
         <v>0</v>
       </c>
       <c r="I190" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J190" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A191" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>482</v>
@@ -8009,7 +8009,7 @@
         <v>7</v>
       </c>
       <c r="F191" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>482</v>
@@ -8021,15 +8021,15 @@
         <v>7</v>
       </c>
       <c r="J191" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A192" s="2" t="s">
-        <v>433</v>
+        <v>241</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>198</v>
+        <v>5</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>482</v>
@@ -8041,7 +8041,7 @@
         <v>7</v>
       </c>
       <c r="F192" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>482</v>
@@ -8050,18 +8050,18 @@
         <v>0</v>
       </c>
       <c r="I192" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J192" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A193" s="2" t="s">
-        <v>241</v>
+        <v>402</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>482</v>
@@ -8073,7 +8073,7 @@
         <v>7</v>
       </c>
       <c r="F193" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>482</v>
@@ -8082,18 +8082,18 @@
         <v>0</v>
       </c>
       <c r="I193" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J193" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A194" s="2" t="s">
-        <v>402</v>
+        <v>322</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>482</v>
@@ -8105,7 +8105,7 @@
         <v>7</v>
       </c>
       <c r="F194" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>482</v>
@@ -8114,18 +8114,18 @@
         <v>0</v>
       </c>
       <c r="I194" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J194" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A195" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>482</v>
@@ -8137,7 +8137,7 @@
         <v>7</v>
       </c>
       <c r="F195" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>482</v>
@@ -8146,18 +8146,18 @@
         <v>0</v>
       </c>
       <c r="I195" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J195" s="3">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A196" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>482</v>
@@ -8169,7 +8169,7 @@
         <v>7</v>
       </c>
       <c r="F196" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>482</v>
@@ -8181,15 +8181,15 @@
         <v>4</v>
       </c>
       <c r="J196" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A197" s="2" t="s">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>482</v>
@@ -8201,7 +8201,7 @@
         <v>7</v>
       </c>
       <c r="F197" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>482</v>
@@ -8210,18 +8210,18 @@
         <v>0</v>
       </c>
       <c r="I197" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J197" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A198" s="2" t="s">
-        <v>290</v>
+        <v>407</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>482</v>
@@ -8233,7 +8233,7 @@
         <v>7</v>
       </c>
       <c r="F198" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>482</v>
@@ -8242,18 +8242,18 @@
         <v>0</v>
       </c>
       <c r="I198" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J198" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A199" s="2" t="s">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>482</v>
@@ -8265,7 +8265,7 @@
         <v>7</v>
       </c>
       <c r="F199" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>482</v>
@@ -8274,18 +8274,18 @@
         <v>0</v>
       </c>
       <c r="I199" s="3">
+        <v>5</v>
+      </c>
+      <c r="J199" s="3">
         <v>6</v>
-      </c>
-      <c r="J199" s="3">
-        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A200" s="2" t="s">
-        <v>361</v>
+        <v>441</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>482</v>
@@ -8297,7 +8297,7 @@
         <v>7</v>
       </c>
       <c r="F200" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>482</v>
@@ -8306,18 +8306,18 @@
         <v>0</v>
       </c>
       <c r="I200" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J200" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A201" s="2" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>482</v>
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="F201" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>482</v>
@@ -8341,15 +8341,15 @@
         <v>7</v>
       </c>
       <c r="J201" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A202" s="2" t="s">
-        <v>417</v>
+        <v>305</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>182</v>
+        <v>71</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>482</v>
@@ -8361,7 +8361,7 @@
         <v>7</v>
       </c>
       <c r="F202" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>482</v>
@@ -8370,18 +8370,18 @@
         <v>0</v>
       </c>
       <c r="I202" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J202" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A203" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>482</v>
@@ -8393,7 +8393,7 @@
         <v>7</v>
       </c>
       <c r="F203" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>482</v>
@@ -8405,15 +8405,15 @@
         <v>3</v>
       </c>
       <c r="J203" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A204" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>482</v>
@@ -8425,7 +8425,7 @@
         <v>7</v>
       </c>
       <c r="F204" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>482</v>
@@ -8437,15 +8437,15 @@
         <v>3</v>
       </c>
       <c r="J204" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A205" s="2" t="s">
-        <v>318</v>
+        <v>449</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>482</v>
@@ -8454,10 +8454,10 @@
         <v>2</v>
       </c>
       <c r="E205" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F205" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>482</v>
@@ -8466,18 +8466,18 @@
         <v>0</v>
       </c>
       <c r="I205" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J205" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A206" s="2" t="s">
-        <v>449</v>
+        <v>273</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>213</v>
+        <v>40</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>482</v>
@@ -8489,7 +8489,7 @@
         <v>8</v>
       </c>
       <c r="F206" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>482</v>
@@ -8498,18 +8498,18 @@
         <v>0</v>
       </c>
       <c r="I206" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J206" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A207" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>482</v>
@@ -8521,7 +8521,7 @@
         <v>8</v>
       </c>
       <c r="F207" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>482</v>
@@ -8530,18 +8530,18 @@
         <v>0</v>
       </c>
       <c r="I207" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J207" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A208" s="2" t="s">
-        <v>253</v>
+        <v>467</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>482</v>
@@ -8553,7 +8553,7 @@
         <v>8</v>
       </c>
       <c r="F208" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>482</v>
@@ -8562,18 +8562,18 @@
         <v>0</v>
       </c>
       <c r="I208" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J208" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A209" s="2" t="s">
-        <v>467</v>
+        <v>319</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>482</v>
@@ -8585,7 +8585,7 @@
         <v>8</v>
       </c>
       <c r="F209" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>482</v>
@@ -8594,18 +8594,18 @@
         <v>0</v>
       </c>
       <c r="I209" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J209" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A210" s="2" t="s">
-        <v>319</v>
+        <v>386</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>482</v>
@@ -8617,7 +8617,7 @@
         <v>8</v>
       </c>
       <c r="F210" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>482</v>
@@ -8626,18 +8626,18 @@
         <v>0</v>
       </c>
       <c r="I210" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J210" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A211" s="2" t="s">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>482</v>
@@ -8649,7 +8649,7 @@
         <v>8</v>
       </c>
       <c r="F211" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>482</v>
@@ -8658,18 +8658,18 @@
         <v>0</v>
       </c>
       <c r="I211" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J211" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A212" s="2" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>482</v>
@@ -8681,7 +8681,7 @@
         <v>8</v>
       </c>
       <c r="F212" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>482</v>
@@ -8690,18 +8690,18 @@
         <v>0</v>
       </c>
       <c r="I212" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J212" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A213" s="2" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>482</v>
@@ -8713,7 +8713,7 @@
         <v>8</v>
       </c>
       <c r="F213" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>482</v>
@@ -8722,18 +8722,18 @@
         <v>0</v>
       </c>
       <c r="I213" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J213" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A214" s="2" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>482</v>
@@ -8745,7 +8745,7 @@
         <v>8</v>
       </c>
       <c r="F214" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>482</v>
@@ -8754,18 +8754,18 @@
         <v>0</v>
       </c>
       <c r="I214" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J214" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A215" s="2" t="s">
-        <v>371</v>
+        <v>283</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>482</v>
@@ -8777,7 +8777,7 @@
         <v>8</v>
       </c>
       <c r="F215" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>482</v>
@@ -8786,18 +8786,18 @@
         <v>0</v>
       </c>
       <c r="I215" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J215" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A216" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>482</v>
@@ -8809,7 +8809,7 @@
         <v>8</v>
       </c>
       <c r="F216" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>482</v>
@@ -8821,15 +8821,15 @@
         <v>2</v>
       </c>
       <c r="J216" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A217" s="2" t="s">
-        <v>272</v>
+        <v>406</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>482</v>
@@ -8841,7 +8841,7 @@
         <v>8</v>
       </c>
       <c r="F217" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>482</v>
@@ -8850,18 +8850,18 @@
         <v>0</v>
       </c>
       <c r="I217" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J217" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A218" s="2" t="s">
-        <v>406</v>
+        <v>252</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>482</v>
@@ -8873,7 +8873,7 @@
         <v>8</v>
       </c>
       <c r="F218" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>482</v>
@@ -8882,18 +8882,18 @@
         <v>0</v>
       </c>
       <c r="I218" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J218" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A219" s="2" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>482</v>
@@ -8905,7 +8905,7 @@
         <v>8</v>
       </c>
       <c r="F219" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>482</v>
@@ -8917,15 +8917,15 @@
         <v>1</v>
       </c>
       <c r="J219" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A220" s="2" t="s">
-        <v>240</v>
+        <v>404</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>4</v>
+        <v>169</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>482</v>
@@ -8937,7 +8937,7 @@
         <v>8</v>
       </c>
       <c r="F220" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>482</v>
@@ -8946,18 +8946,18 @@
         <v>0</v>
       </c>
       <c r="I220" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J220" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A221" s="2" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>482</v>
@@ -8969,7 +8969,7 @@
         <v>8</v>
       </c>
       <c r="F221" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>482</v>
@@ -8978,18 +8978,18 @@
         <v>0</v>
       </c>
       <c r="I221" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J221" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A222" s="2" t="s">
-        <v>451</v>
+        <v>373</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>482</v>
@@ -9001,7 +9001,7 @@
         <v>8</v>
       </c>
       <c r="F222" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>482</v>
@@ -9010,18 +9010,18 @@
         <v>0</v>
       </c>
       <c r="I222" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J222" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A223" s="2" t="s">
-        <v>373</v>
+        <v>455</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>482</v>
@@ -9033,7 +9033,7 @@
         <v>8</v>
       </c>
       <c r="F223" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>482</v>
@@ -9042,18 +9042,18 @@
         <v>0</v>
       </c>
       <c r="I223" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J223" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A224" s="2" t="s">
-        <v>455</v>
+        <v>347</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>219</v>
+        <v>113</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>482</v>
@@ -9065,7 +9065,7 @@
         <v>8</v>
       </c>
       <c r="F224" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>482</v>
@@ -9074,18 +9074,18 @@
         <v>0</v>
       </c>
       <c r="I224" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J224" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A225" s="2" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>482</v>
@@ -9097,7 +9097,7 @@
         <v>8</v>
       </c>
       <c r="F225" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>482</v>
@@ -9106,18 +9106,18 @@
         <v>0</v>
       </c>
       <c r="I225" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J225" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A226" s="2" t="s">
-        <v>258</v>
+        <v>414</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>482</v>
@@ -9129,7 +9129,7 @@
         <v>8</v>
       </c>
       <c r="F226" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>482</v>
@@ -9138,18 +9138,18 @@
         <v>0</v>
       </c>
       <c r="I226" s="3">
+        <v>7</v>
+      </c>
+      <c r="J226" s="3">
         <v>1</v>
-      </c>
-      <c r="J226" s="3">
-        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A227" s="2" t="s">
-        <v>414</v>
+        <v>249</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>482</v>
@@ -9161,7 +9161,7 @@
         <v>8</v>
       </c>
       <c r="F227" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>482</v>
@@ -9170,18 +9170,18 @@
         <v>0</v>
       </c>
       <c r="I227" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J227" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A228" s="2" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>482</v>
@@ -9193,7 +9193,7 @@
         <v>8</v>
       </c>
       <c r="F228" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>482</v>
@@ -9202,18 +9202,18 @@
         <v>0</v>
       </c>
       <c r="I228" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J228" s="3">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A229" s="2" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>482</v>
@@ -9225,7 +9225,7 @@
         <v>8</v>
       </c>
       <c r="F229" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>482</v>
@@ -9234,18 +9234,18 @@
         <v>0</v>
       </c>
       <c r="I229" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J229" s="3">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A230" s="2" t="s">
-        <v>301</v>
+        <v>393</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>482</v>
@@ -9257,7 +9257,7 @@
         <v>8</v>
       </c>
       <c r="F230" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>482</v>
@@ -9266,18 +9266,18 @@
         <v>0</v>
       </c>
       <c r="I230" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J230" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A231" s="2" t="s">
-        <v>393</v>
+        <v>295</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>159</v>
+        <v>61</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>482</v>
@@ -9289,7 +9289,7 @@
         <v>8</v>
       </c>
       <c r="F231" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>482</v>
@@ -9298,18 +9298,18 @@
         <v>0</v>
       </c>
       <c r="I231" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J231" s="3">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A232" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>482</v>
@@ -9321,7 +9321,7 @@
         <v>8</v>
       </c>
       <c r="F232" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>482</v>
@@ -9333,28 +9333,24 @@
         <v>2</v>
       </c>
       <c r="J232" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A233" s="2" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>482</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E233" s="3">
-        <v>8</v>
-      </c>
-      <c r="F233" s="3">
-        <v>28</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E233" s="3"/>
+      <c r="F233" s="3"/>
       <c r="G233" s="2" t="s">
         <v>482</v>
       </c>
@@ -9362,24 +9358,24 @@
         <v>0</v>
       </c>
       <c r="I233" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J233" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A234" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>482</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
@@ -9393,21 +9389,21 @@
         <v>1</v>
       </c>
       <c r="J234" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A235" s="2" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>482</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
@@ -9418,24 +9414,24 @@
         <v>0</v>
       </c>
       <c r="I235" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J235" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A236" s="2" t="s">
-        <v>306</v>
+        <v>403</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>482</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
@@ -9446,16 +9442,16 @@
         <v>0</v>
       </c>
       <c r="I236" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J236" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J236">
-    <sortCondition ref="E2:E236"/>
-    <sortCondition ref="F2:F236"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J235">
+    <sortCondition ref="E2:E235"/>
+    <sortCondition ref="F2:F235"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
